--- a/Gored BOM.xlsx
+++ b/Gored BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\povseaa\Documents\GitHub\30lb-Capstone-Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66B66950-C813-4EBF-B694-8AECEF7F39FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80BC487-DC11-45BC-B83B-02769B30CC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2E6AAB31-3DD4-45E3-978E-4A2557BFC82A}"/>
   </bookViews>
@@ -33,6 +33,161 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Part Name</t>
+  </si>
+  <si>
+    <t>Price Ea</t>
+  </si>
+  <si>
+    <t>Weight Ea (g)</t>
+  </si>
+  <si>
+    <t>Total Weight</t>
+  </si>
+  <si>
+    <t>Total Price</t>
+  </si>
+  <si>
+    <t>Spares</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Subsystem</t>
+  </si>
+  <si>
+    <t>Frame</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>QTY On Bot</t>
+  </si>
+  <si>
+    <t>QTY Total</t>
+  </si>
+  <si>
+    <t>Left Drive Rail</t>
+  </si>
+  <si>
+    <t>Right Drive Rail</t>
+  </si>
+  <si>
+    <t>Left Front wall</t>
+  </si>
+  <si>
+    <t>Right Front Wall</t>
+  </si>
+  <si>
+    <t>Left Upright</t>
+  </si>
+  <si>
+    <t>Right Upright</t>
+  </si>
+  <si>
+    <t>Backplate</t>
+  </si>
+  <si>
+    <t>Side Guard Front Mount</t>
+  </si>
+  <si>
+    <t>Side Guard Back Mount</t>
+  </si>
+  <si>
+    <t>Carbon Bottom Plate</t>
+  </si>
+  <si>
+    <t>1/4" Aluminum</t>
+  </si>
+  <si>
+    <t>SEP</t>
+  </si>
+  <si>
+    <t>Ask tom, BIC Worker works for this company and can get good deal</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>14mm AR600 Weapon</t>
+  </si>
+  <si>
+    <t>1/2" AR500 Weapon</t>
+  </si>
+  <si>
+    <t>Weapon Hub</t>
+  </si>
+  <si>
+    <t>Weapon Shaft</t>
+  </si>
+  <si>
+    <t>Needle Roller Bearings</t>
+  </si>
+  <si>
+    <t>Weapon Bolts</t>
+  </si>
+  <si>
+    <t>Orange Side Plates</t>
+  </si>
+  <si>
+    <t>Drive</t>
+  </si>
+  <si>
+    <t>Front Wheels</t>
+  </si>
+  <si>
+    <t>Rear Wheels</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Main Power Switch</t>
+  </si>
+  <si>
+    <t>Reciever Power Switch</t>
+  </si>
+  <si>
+    <t>Drive Motor</t>
+  </si>
+  <si>
+    <t>Weapon Motor</t>
+  </si>
+  <si>
+    <t>Weapon ESC</t>
+  </si>
+  <si>
+    <t>Drive ESC</t>
+  </si>
+  <si>
+    <t>Castle 1515</t>
+  </si>
+  <si>
+    <t>ER4</t>
+  </si>
+  <si>
+    <t>Reciever</t>
+  </si>
+  <si>
+    <t>Weapon Belt</t>
+  </si>
+  <si>
+    <t>Drive Axel</t>
+  </si>
+  <si>
+    <t>Bushing</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +557,479 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882F98A2-994E-4BEF-902F-AF30D0FF4095}">
-  <dimension ref="A1"/>
+  <dimension ref="A3:L45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <f>D4-C4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I12" si="0">D5-C5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <f>D13-C13</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <f>D14-C14</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="K30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Gored BOM.xlsx
+++ b/Gored BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\povseaa\Documents\GitHub\30lb-Capstone-Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80BC487-DC11-45BC-B83B-02769B30CC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C70EFE-689E-4460-B15D-33F86D6A09FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2E6AAB31-3DD4-45E3-978E-4A2557BFC82A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>Link</t>
   </si>
@@ -186,6 +186,39 @@
   </si>
   <si>
     <t>Bushing</t>
+  </si>
+  <si>
+    <t>Main Battery</t>
+  </si>
+  <si>
+    <t>Reciever Battery</t>
+  </si>
+  <si>
+    <t>3s 380</t>
+  </si>
+  <si>
+    <t>https://www.gaoneng.shop/products/gaoneng-gnb-6s-22.2v-1850mah-100c-xt60-lipo-battery</t>
+  </si>
+  <si>
+    <t>6s 1850</t>
+  </si>
+  <si>
+    <t>Drive Belt Short</t>
+  </si>
+  <si>
+    <t>Drive Belt Long</t>
+  </si>
+  <si>
+    <t>GNB</t>
+  </si>
+  <si>
+    <t>Radiomaster</t>
+  </si>
+  <si>
+    <t>Drive Pulley</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
@@ -238,6 +271,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D4A082E-55D1-4EBF-B523-76D8593A9EB4}" name="Table1" displayName="Table1" ref="A1:L44" totalsRowShown="0">
+  <autoFilter ref="A1:L44" xr:uid="{1D4A082E-55D1-4EBF-B523-76D8593A9EB4}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9A262696-EEC3-4668-A729-7A8CB9247DE8}" name="Subsystem"/>
+    <tableColumn id="2" xr3:uid="{A07EEDA7-C62D-492B-B58F-8BE45C7992A3}" name="Part Name"/>
+    <tableColumn id="3" xr3:uid="{A3F7DCD5-94A1-4DDC-AA27-ABC0BB550BBB}" name="QTY On Bot"/>
+    <tableColumn id="4" xr3:uid="{6AD45A61-2FF8-4084-BC63-4CA9BB3BDBD4}" name="QTY Total"/>
+    <tableColumn id="5" xr3:uid="{F3A4A91A-ED98-4CA1-971F-C5E7322827C2}" name="Price Ea"/>
+    <tableColumn id="6" xr3:uid="{1115EAA2-9AC2-4559-83D1-31362E934CE2}" name="Weight Ea (g)"/>
+    <tableColumn id="7" xr3:uid="{A3AC107C-939B-43EB-92F3-D26CBDECBF37}" name="Total Weight"/>
+    <tableColumn id="8" xr3:uid="{FD1D1108-8666-4A41-BD5E-8AC05CD11FE1}" name="Total Price"/>
+    <tableColumn id="9" xr3:uid="{91B3CB33-B4C3-4924-83EE-4AEB55C7E3D9}" name="Spares"/>
+    <tableColumn id="10" xr3:uid="{048AA429-428F-4451-B59C-BE85FE3D1B4C}" name="Vendor"/>
+    <tableColumn id="11" xr3:uid="{591599D4-26FA-4EE7-BD4D-2336868535F2}" name="Notes"/>
+    <tableColumn id="12" xr3:uid="{16DBD91C-00EE-490D-B493-27283CF1FA90}" name="Link"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -557,55 +611,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882F98A2-994E-4BEF-902F-AF30D0FF4095}">
-  <dimension ref="A3:L45"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="47" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>D2-C2</f>
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" t="s">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I10" si="0">D3-C3</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -613,23 +711,17 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <f>D4-C4</f>
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -637,7 +729,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -646,7 +738,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:I12" si="0">D5-C5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -655,7 +747,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -673,7 +765,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -691,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -709,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -727,17 +819,14 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
         <v>2</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -745,17 +834,14 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
         <v>2</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>D11-C11</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -763,55 +849,53 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <f>D13-C13</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="I14">
-        <f>D14-C14</f>
+        <f>D12-C12</f>
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -820,123 +904,150 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
-      </c>
-      <c r="K30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>58</v>
+      </c>
+      <c r="K31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>50</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="J32" t="s">
+        <v>57</v>
+      </c>
+      <c r="K32" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -944,10 +1055,16 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>57</v>
       </c>
       <c r="K33" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -955,14 +1072,26 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-    </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -970,7 +1099,7 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -981,7 +1110,7 @@
         <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -991,6 +1120,12 @@
       <c r="A40" t="s">
         <v>34</v>
       </c>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -1001,35 +1136,28 @@
       <c r="A42" t="s">
         <v>34</v>
       </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="B43" t="s">
         <v>49</v>
       </c>
-      <c r="C45">
+      <c r="C43">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Gored BOM.xlsx
+++ b/Gored BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\povseaa\Documents\GitHub\30lb-Capstone-Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C70EFE-689E-4460-B15D-33F86D6A09FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8581E0-616B-4298-9B63-3A8A9659A7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2E6AAB31-3DD4-45E3-978E-4A2557BFC82A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>Link</t>
   </si>
@@ -219,16 +219,46 @@
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>190-5m-09</t>
+  </si>
+  <si>
+    <t>140J6 - D&amp;D Dura-Prime Multi-Ribbed Poly V-Belt – Compressor Components</t>
+  </si>
+  <si>
+    <t>140J6 (135 might be better)</t>
+  </si>
+  <si>
+    <t>Castle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -251,16 +281,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -281,10 +327,12 @@
     <tableColumn id="2" xr3:uid="{A07EEDA7-C62D-492B-B58F-8BE45C7992A3}" name="Part Name"/>
     <tableColumn id="3" xr3:uid="{A3F7DCD5-94A1-4DDC-AA27-ABC0BB550BBB}" name="QTY On Bot"/>
     <tableColumn id="4" xr3:uid="{6AD45A61-2FF8-4084-BC63-4CA9BB3BDBD4}" name="QTY Total"/>
-    <tableColumn id="5" xr3:uid="{F3A4A91A-ED98-4CA1-971F-C5E7322827C2}" name="Price Ea"/>
+    <tableColumn id="5" xr3:uid="{F3A4A91A-ED98-4CA1-971F-C5E7322827C2}" name="Price Ea" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{FD1D1108-8666-4A41-BD5E-8AC05CD11FE1}" name="Total Price" dataDxfId="0">
+      <calculatedColumnFormula>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="6" xr3:uid="{1115EAA2-9AC2-4559-83D1-31362E934CE2}" name="Weight Ea (g)"/>
     <tableColumn id="7" xr3:uid="{A3AC107C-939B-43EB-92F3-D26CBDECBF37}" name="Total Weight"/>
-    <tableColumn id="8" xr3:uid="{FD1D1108-8666-4A41-BD5E-8AC05CD11FE1}" name="Total Price"/>
     <tableColumn id="9" xr3:uid="{91B3CB33-B4C3-4924-83EE-4AEB55C7E3D9}" name="Spares"/>
     <tableColumn id="10" xr3:uid="{048AA429-428F-4451-B59C-BE85FE3D1B4C}" name="Vendor"/>
     <tableColumn id="11" xr3:uid="{591599D4-26FA-4EE7-BD4D-2336868535F2}" name="Notes"/>
@@ -611,18 +659,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882F98A2-994E-4BEF-902F-AF30D0FF4095}">
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" customWidth="1"/>
     <col min="8" max="8" width="11.21875" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.109375" customWidth="1"/>
     <col min="12" max="12" width="47" customWidth="1"/>
   </cols>
   <sheetData>
@@ -639,17 +688,17 @@
       <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -677,6 +726,10 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I2">
         <f>D2-C2</f>
         <v>0</v>
@@ -701,6 +754,10 @@
       <c r="D3">
         <v>2</v>
       </c>
+      <c r="F3" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I3">
         <f t="shared" ref="I3:I10" si="0">D3-C3</f>
         <v>1</v>
@@ -719,6 +776,10 @@
       <c r="D4">
         <v>2</v>
       </c>
+      <c r="F4" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I4">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -737,6 +798,10 @@
       <c r="D5">
         <v>2</v>
       </c>
+      <c r="F5" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I5">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -755,6 +820,10 @@
       <c r="D6">
         <v>2</v>
       </c>
+      <c r="F6" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I6">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -773,6 +842,10 @@
       <c r="D7">
         <v>2</v>
       </c>
+      <c r="F7" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I7">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -791,6 +864,10 @@
       <c r="D8">
         <v>2</v>
       </c>
+      <c r="F8" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I8">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -809,6 +886,10 @@
       <c r="D9">
         <v>2</v>
       </c>
+      <c r="F9" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I9">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -824,6 +905,10 @@
       <c r="C10">
         <v>2</v>
       </c>
+      <c r="F10" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I10">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -839,6 +924,10 @@
       <c r="C11">
         <v>2</v>
       </c>
+      <c r="F11" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I11">
         <f>D11-C11</f>
         <v>-2</v>
@@ -857,11 +946,27 @@
       <c r="D12">
         <v>4</v>
       </c>
+      <c r="F12" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="I12">
         <f>D12-C12</f>
         <v>3</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F13" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F14" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
@@ -875,6 +980,10 @@
       <c r="D15">
         <v>2</v>
       </c>
+      <c r="F15" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -884,9 +993,13 @@
         <v>28</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
         <v>0</v>
       </c>
     </row>
@@ -903,6 +1016,10 @@
       <c r="D17">
         <v>2</v>
       </c>
+      <c r="F17" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -911,6 +1028,10 @@
       <c r="B18" t="s">
         <v>30</v>
       </c>
+      <c r="F18" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -919,6 +1040,10 @@
       <c r="B19" t="s">
         <v>31</v>
       </c>
+      <c r="F19" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -927,6 +1052,10 @@
       <c r="B20" t="s">
         <v>32</v>
       </c>
+      <c r="F20" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -935,6 +1064,10 @@
       <c r="B21" t="s">
         <v>33</v>
       </c>
+      <c r="F21" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -943,6 +1076,28 @@
       <c r="B22" t="s">
         <v>47</v>
       </c>
+      <c r="F22" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>63</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F23" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F24" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -954,6 +1109,10 @@
       <c r="C25">
         <v>1</v>
       </c>
+      <c r="F25" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -965,6 +1124,10 @@
       <c r="C26">
         <v>1</v>
       </c>
+      <c r="F26" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -976,6 +1139,10 @@
       <c r="C27">
         <v>2</v>
       </c>
+      <c r="F27" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -987,6 +1154,16 @@
       <c r="C28">
         <v>1</v>
       </c>
+      <c r="E28" s="1">
+        <v>200</v>
+      </c>
+      <c r="F28" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>200</v>
+      </c>
+      <c r="J28" t="s">
+        <v>64</v>
+      </c>
       <c r="K28" t="s">
         <v>44</v>
       </c>
@@ -1001,6 +1178,10 @@
       <c r="C29">
         <v>1</v>
       </c>
+      <c r="F29" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1012,6 +1193,10 @@
       <c r="C30">
         <v>2</v>
       </c>
+      <c r="F30" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1023,6 +1208,10 @@
       <c r="C31">
         <v>2</v>
       </c>
+      <c r="F31" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="J31" t="s">
         <v>58</v>
       </c>
@@ -1040,6 +1229,14 @@
       <c r="C32">
         <v>2</v>
       </c>
+      <c r="E32" s="1">
+        <f>84/2</f>
+        <v>42</v>
+      </c>
+      <c r="F32" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>84</v>
+      </c>
       <c r="J32" t="s">
         <v>57</v>
       </c>
@@ -1060,6 +1257,13 @@
       <c r="C33">
         <v>1</v>
       </c>
+      <c r="E33" s="1">
+        <v>9</v>
+      </c>
+      <c r="F33" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>9</v>
+      </c>
       <c r="J33" t="s">
         <v>57</v>
       </c>
@@ -1071,6 +1275,16 @@
       <c r="A34" t="s">
         <v>37</v>
       </c>
+      <c r="F34" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F35" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -1082,6 +1296,10 @@
       <c r="C36">
         <v>2</v>
       </c>
+      <c r="F36" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -1093,6 +1311,10 @@
       <c r="C37">
         <v>2</v>
       </c>
+      <c r="F37" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -1104,6 +1326,13 @@
       <c r="C38">
         <v>2</v>
       </c>
+      <c r="F38" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -1115,6 +1344,10 @@
       <c r="C39">
         <v>2</v>
       </c>
+      <c r="F39" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1123,6 +1356,10 @@
       <c r="B40" t="s">
         <v>59</v>
       </c>
+      <c r="F40" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
       <c r="J40" t="s">
         <v>60</v>
       </c>
@@ -1131,6 +1368,10 @@
       <c r="A41" t="s">
         <v>34</v>
       </c>
+      <c r="F41" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -1142,6 +1383,10 @@
       <c r="C42">
         <v>4</v>
       </c>
+      <c r="F42" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -1153,11 +1398,25 @@
       <c r="C43">
         <v>4</v>
       </c>
+      <c r="F43" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F44" s="2">
+        <f>Table1[[#This Row],[Price Ea]]*Table1[[#This Row],[QTY On Bot]]</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L22" r:id="rId1" display="https://compressorcomponents.com/products/140j6" xr:uid="{C4317AF8-7E9E-431E-95E2-CAA348CFB00A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>